--- a/artfynd/A 34275-2025 artfynd.xlsx
+++ b/artfynd/A 34275-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126600734</v>
+        <v>126600738</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>4772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507916</v>
+        <v>507958</v>
       </c>
       <c r="R3" t="n">
-        <v>6542579</v>
+        <v>6542499</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -892,7 +892,7 @@
         <v>126601043</v>
       </c>
       <c r="B4" t="n">
-        <v>96650</v>
+        <v>96725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126600738</v>
+        <v>126600734</v>
       </c>
       <c r="B5" t="n">
-        <v>4772</v>
+        <v>8447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507958</v>
+        <v>507916</v>
       </c>
       <c r="R5" t="n">
-        <v>6542499</v>
+        <v>6542579</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1316,7 +1316,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126600699</v>
+        <v>126601064</v>
       </c>
       <c r="B8" t="n">
         <v>8447</v>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507819</v>
+        <v>507727</v>
       </c>
       <c r="R8" t="n">
-        <v>6542586</v>
+        <v>6542229</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126601064</v>
+        <v>126600699</v>
       </c>
       <c r="B9" t="n">
         <v>8447</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507727</v>
+        <v>507819</v>
       </c>
       <c r="R9" t="n">
-        <v>6542229</v>
+        <v>6542586</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1637,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126601040</v>
+        <v>126600962</v>
       </c>
       <c r="B11" t="n">
-        <v>8447</v>
+        <v>96725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,32 +1648,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1681,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507921</v>
+        <v>507910</v>
       </c>
       <c r="R11" t="n">
-        <v>6542284</v>
+        <v>6542329</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1744,41 +1743,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126600806</v>
+        <v>126600795</v>
       </c>
       <c r="B12" t="n">
-        <v>75067</v>
+        <v>5196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>308</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1786,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507912</v>
+        <v>507919</v>
       </c>
       <c r="R12" t="n">
-        <v>6542410</v>
+        <v>6542420</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1849,42 +1850,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126600962</v>
+        <v>126600806</v>
       </c>
       <c r="B13" t="n">
-        <v>96650</v>
+        <v>75127</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2590</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507910</v>
+        <v>507912</v>
       </c>
       <c r="R13" t="n">
-        <v>6542329</v>
+        <v>6542410</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1955,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126600795</v>
+        <v>126601040</v>
       </c>
       <c r="B14" t="n">
-        <v>5196</v>
+        <v>8447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1966,21 +1966,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507919</v>
+        <v>507921</v>
       </c>
       <c r="R14" t="n">
-        <v>6542420</v>
+        <v>6542284</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126600693</v>
+        <v>126600761</v>
       </c>
       <c r="B15" t="n">
-        <v>4772</v>
+        <v>6271</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,32 +2073,32 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100299</v>
+        <v>105336</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507845</v>
+        <v>507954</v>
       </c>
       <c r="R15" t="n">
-        <v>6542442</v>
+        <v>6542455</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126600761</v>
+        <v>126600693</v>
       </c>
       <c r="B16" t="n">
-        <v>6271</v>
+        <v>4772</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2180,32 +2180,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105336</v>
+        <v>100299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507954</v>
+        <v>507845</v>
       </c>
       <c r="R16" t="n">
-        <v>6542455</v>
+        <v>6542442</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -3025,7 +3025,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126600902</v>
+        <v>126600785</v>
       </c>
       <c r="B24" t="n">
         <v>8447</v>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507934</v>
+        <v>507909</v>
       </c>
       <c r="R24" t="n">
-        <v>6542308</v>
+        <v>6542421</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126600785</v>
+        <v>126600902</v>
       </c>
       <c r="B25" t="n">
         <v>8447</v>
@@ -3176,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507909</v>
+        <v>507934</v>
       </c>
       <c r="R25" t="n">
-        <v>6542421</v>
+        <v>6542308</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>

--- a/artfynd/A 34275-2025 artfynd.xlsx
+++ b/artfynd/A 34275-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126600738</v>
+        <v>126600734</v>
       </c>
       <c r="B3" t="n">
-        <v>4772</v>
+        <v>8447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507958</v>
+        <v>507916</v>
       </c>
       <c r="R3" t="n">
-        <v>6542499</v>
+        <v>6542579</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -892,7 +892,7 @@
         <v>126601043</v>
       </c>
       <c r="B4" t="n">
-        <v>96725</v>
+        <v>96731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126600734</v>
+        <v>126600738</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>4772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507916</v>
+        <v>507958</v>
       </c>
       <c r="R5" t="n">
-        <v>6542579</v>
+        <v>6542499</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126600779</v>
+        <v>126601064</v>
       </c>
       <c r="B7" t="n">
-        <v>4772</v>
+        <v>8447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,21 +1220,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507911</v>
+        <v>507727</v>
       </c>
       <c r="R7" t="n">
-        <v>6542433</v>
+        <v>6542229</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1316,7 +1316,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126601064</v>
+        <v>126600699</v>
       </c>
       <c r="B8" t="n">
         <v>8447</v>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507727</v>
+        <v>507819</v>
       </c>
       <c r="R8" t="n">
-        <v>6542229</v>
+        <v>6542586</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126600699</v>
+        <v>126600779</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
+        <v>4772</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,21 +1434,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507819</v>
+        <v>507911</v>
       </c>
       <c r="R9" t="n">
-        <v>6542586</v>
+        <v>6542433</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1637,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126600962</v>
+        <v>126600795</v>
       </c>
       <c r="B11" t="n">
-        <v>96725</v>
+        <v>5196</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,31 +1648,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2590</v>
+        <v>105930</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,10 +1681,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507910</v>
+        <v>507919</v>
       </c>
       <c r="R11" t="n">
-        <v>6542329</v>
+        <v>6542420</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1743,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126600795</v>
+        <v>126601040</v>
       </c>
       <c r="B12" t="n">
-        <v>5196</v>
+        <v>8447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1754,21 +1755,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1787,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507919</v>
+        <v>507921</v>
       </c>
       <c r="R12" t="n">
-        <v>6542420</v>
+        <v>6542284</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1853,7 +1854,7 @@
         <v>126600806</v>
       </c>
       <c r="B13" t="n">
-        <v>75127</v>
+        <v>75130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1955,10 +1956,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126601040</v>
+        <v>126600962</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>96731</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1966,32 +1967,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507921</v>
+        <v>507910</v>
       </c>
       <c r="R14" t="n">
-        <v>6542284</v>
+        <v>6542329</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126600761</v>
+        <v>126600693</v>
       </c>
       <c r="B15" t="n">
-        <v>6271</v>
+        <v>4772</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,32 +2073,32 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>105336</v>
+        <v>100299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507954</v>
+        <v>507845</v>
       </c>
       <c r="R15" t="n">
-        <v>6542455</v>
+        <v>6542442</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126600693</v>
+        <v>126600761</v>
       </c>
       <c r="B16" t="n">
-        <v>4772</v>
+        <v>6271</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2180,32 +2180,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100299</v>
+        <v>105336</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507845</v>
+        <v>507954</v>
       </c>
       <c r="R16" t="n">
-        <v>6542442</v>
+        <v>6542455</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126600697</v>
+        <v>126600873</v>
       </c>
       <c r="B22" t="n">
-        <v>8447</v>
+        <v>6271</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2822,32 +2822,32 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>105336</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507831</v>
+        <v>507957</v>
       </c>
       <c r="R22" t="n">
-        <v>6542470</v>
+        <v>6542361</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126600873</v>
+        <v>126600697</v>
       </c>
       <c r="B23" t="n">
-        <v>6271</v>
+        <v>8447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2929,32 +2929,32 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105336</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507957</v>
+        <v>507831</v>
       </c>
       <c r="R23" t="n">
-        <v>6542361</v>
+        <v>6542470</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>

--- a/artfynd/A 34275-2025 artfynd.xlsx
+++ b/artfynd/A 34275-2025 artfynd.xlsx
@@ -1209,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126601064</v>
+        <v>126600779</v>
       </c>
       <c r="B7" t="n">
-        <v>8447</v>
+        <v>4772</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,21 +1220,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1253,10 +1253,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507727</v>
+        <v>507911</v>
       </c>
       <c r="R7" t="n">
-        <v>6542229</v>
+        <v>6542433</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1423,10 +1423,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126600779</v>
+        <v>126601064</v>
       </c>
       <c r="B9" t="n">
-        <v>4772</v>
+        <v>8447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,21 +1434,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507911</v>
+        <v>507727</v>
       </c>
       <c r="R9" t="n">
-        <v>6542433</v>
+        <v>6542229</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1637,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126600795</v>
+        <v>126600962</v>
       </c>
       <c r="B11" t="n">
-        <v>5196</v>
+        <v>96731</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,32 +1648,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>105930</v>
+        <v>2590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1681,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507919</v>
+        <v>507910</v>
       </c>
       <c r="R11" t="n">
-        <v>6542420</v>
+        <v>6542329</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1744,43 +1743,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126601040</v>
+        <v>126600806</v>
       </c>
       <c r="B12" t="n">
-        <v>8447</v>
+        <v>75130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1788,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507921</v>
+        <v>507912</v>
       </c>
       <c r="R12" t="n">
-        <v>6542284</v>
+        <v>6542410</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1851,41 +1848,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126600806</v>
+        <v>126600795</v>
       </c>
       <c r="B13" t="n">
-        <v>75130</v>
+        <v>5196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1893,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507912</v>
+        <v>507919</v>
       </c>
       <c r="R13" t="n">
-        <v>6542410</v>
+        <v>6542420</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1956,10 +1955,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126600962</v>
+        <v>126601040</v>
       </c>
       <c r="B14" t="n">
-        <v>96731</v>
+        <v>8447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1967,31 +1966,32 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2590</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507910</v>
+        <v>507921</v>
       </c>
       <c r="R14" t="n">
-        <v>6542329</v>
+        <v>6542284</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2062,10 +2062,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126600693</v>
+        <v>126600761</v>
       </c>
       <c r="B15" t="n">
-        <v>4772</v>
+        <v>6271</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,32 +2073,32 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100299</v>
+        <v>105336</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507845</v>
+        <v>507954</v>
       </c>
       <c r="R15" t="n">
-        <v>6542442</v>
+        <v>6542455</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2169,10 +2169,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126600761</v>
+        <v>126600693</v>
       </c>
       <c r="B16" t="n">
-        <v>6271</v>
+        <v>4772</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2180,32 +2180,32 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105336</v>
+        <v>100299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507954</v>
+        <v>507845</v>
       </c>
       <c r="R16" t="n">
-        <v>6542455</v>
+        <v>6542442</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2597,7 +2597,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126600741</v>
+        <v>126600750</v>
       </c>
       <c r="B20" t="n">
         <v>8447</v>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507957</v>
+        <v>507956</v>
       </c>
       <c r="R20" t="n">
-        <v>6542483</v>
+        <v>6542468</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2704,7 +2704,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126600750</v>
+        <v>126600741</v>
       </c>
       <c r="B21" t="n">
         <v>8447</v>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507956</v>
+        <v>507957</v>
       </c>
       <c r="R21" t="n">
-        <v>6542468</v>
+        <v>6542483</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2811,10 +2811,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126600873</v>
+        <v>126600697</v>
       </c>
       <c r="B22" t="n">
-        <v>6271</v>
+        <v>8447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2822,32 +2822,32 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105336</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507957</v>
+        <v>507831</v>
       </c>
       <c r="R22" t="n">
-        <v>6542361</v>
+        <v>6542470</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2918,10 +2918,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126600697</v>
+        <v>126600873</v>
       </c>
       <c r="B23" t="n">
-        <v>8447</v>
+        <v>6271</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2929,32 +2929,32 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>105336</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2962,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>507831</v>
+        <v>507957</v>
       </c>
       <c r="R23" t="n">
-        <v>6542470</v>
+        <v>6542361</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>

--- a/artfynd/A 34275-2025 artfynd.xlsx
+++ b/artfynd/A 34275-2025 artfynd.xlsx
@@ -3349,7 +3349,7 @@
         <v>126671977</v>
       </c>
       <c r="B27" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>126674072</v>
       </c>
       <c r="B28" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>126674690</v>
       </c>
       <c r="B29" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34275-2025 artfynd.xlsx
+++ b/artfynd/A 34275-2025 artfynd.xlsx
@@ -3349,7 +3349,7 @@
         <v>126671977</v>
       </c>
       <c r="B27" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>126674072</v>
       </c>
       <c r="B28" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>126674690</v>
       </c>
       <c r="B29" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34275-2025 artfynd.xlsx
+++ b/artfynd/A 34275-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126600734</v>
+        <v>126600738</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>4772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507916</v>
+        <v>507958</v>
       </c>
       <c r="R3" t="n">
-        <v>6542579</v>
+        <v>6542499</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -892,7 +892,7 @@
         <v>126601043</v>
       </c>
       <c r="B4" t="n">
-        <v>96731</v>
+        <v>96725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126600738</v>
+        <v>126600734</v>
       </c>
       <c r="B5" t="n">
-        <v>4772</v>
+        <v>8447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507958</v>
+        <v>507916</v>
       </c>
       <c r="R5" t="n">
-        <v>6542499</v>
+        <v>6542579</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1316,7 +1316,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126600699</v>
+        <v>126601064</v>
       </c>
       <c r="B8" t="n">
         <v>8447</v>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507819</v>
+        <v>507727</v>
       </c>
       <c r="R8" t="n">
-        <v>6542586</v>
+        <v>6542229</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126601064</v>
+        <v>126600699</v>
       </c>
       <c r="B9" t="n">
         <v>8447</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507727</v>
+        <v>507819</v>
       </c>
       <c r="R9" t="n">
-        <v>6542229</v>
+        <v>6542586</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1640,7 +1640,7 @@
         <v>126600962</v>
       </c>
       <c r="B11" t="n">
-        <v>96731</v>
+        <v>96725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,41 +1743,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126600806</v>
+        <v>126600795</v>
       </c>
       <c r="B12" t="n">
-        <v>75130</v>
+        <v>5196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>308</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1785,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507912</v>
+        <v>507919</v>
       </c>
       <c r="R12" t="n">
-        <v>6542410</v>
+        <v>6542420</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1848,43 +1850,41 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126600795</v>
+        <v>126600806</v>
       </c>
       <c r="B13" t="n">
-        <v>5196</v>
+        <v>75127</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507919</v>
+        <v>507912</v>
       </c>
       <c r="R13" t="n">
-        <v>6542420</v>
+        <v>6542410</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2597,7 +2597,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126600750</v>
+        <v>126600741</v>
       </c>
       <c r="B20" t="n">
         <v>8447</v>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507956</v>
+        <v>507957</v>
       </c>
       <c r="R20" t="n">
-        <v>6542468</v>
+        <v>6542483</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2704,7 +2704,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126600741</v>
+        <v>126600750</v>
       </c>
       <c r="B21" t="n">
         <v>8447</v>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507957</v>
+        <v>507956</v>
       </c>
       <c r="R21" t="n">
-        <v>6542483</v>
+        <v>6542468</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3349,7 +3349,7 @@
         <v>126671977</v>
       </c>
       <c r="B27" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>126674072</v>
       </c>
       <c r="B28" t="n">
-        <v>56855</v>
+        <v>56849</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>126674690</v>
       </c>
       <c r="B29" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34275-2025 artfynd.xlsx
+++ b/artfynd/A 34275-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126600738</v>
+        <v>126600734</v>
       </c>
       <c r="B3" t="n">
-        <v>4772</v>
+        <v>8447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507958</v>
+        <v>507916</v>
       </c>
       <c r="R3" t="n">
-        <v>6542499</v>
+        <v>6542579</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -892,7 +892,7 @@
         <v>126601043</v>
       </c>
       <c r="B4" t="n">
-        <v>96725</v>
+        <v>96731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126600734</v>
+        <v>126600738</v>
       </c>
       <c r="B5" t="n">
-        <v>8447</v>
+        <v>4772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,21 +1006,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507916</v>
+        <v>507958</v>
       </c>
       <c r="R5" t="n">
-        <v>6542579</v>
+        <v>6542499</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1316,7 +1316,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126601064</v>
+        <v>126600699</v>
       </c>
       <c r="B8" t="n">
         <v>8447</v>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507727</v>
+        <v>507819</v>
       </c>
       <c r="R8" t="n">
-        <v>6542229</v>
+        <v>6542586</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1423,7 +1423,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126600699</v>
+        <v>126601064</v>
       </c>
       <c r="B9" t="n">
         <v>8447</v>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507819</v>
+        <v>507727</v>
       </c>
       <c r="R9" t="n">
-        <v>6542586</v>
+        <v>6542229</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1640,7 +1640,7 @@
         <v>126600962</v>
       </c>
       <c r="B11" t="n">
-        <v>96725</v>
+        <v>96731</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,43 +1743,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126600795</v>
+        <v>126600806</v>
       </c>
       <c r="B12" t="n">
-        <v>5196</v>
+        <v>75130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>105930</v>
+        <v>308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1787,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507919</v>
+        <v>507912</v>
       </c>
       <c r="R12" t="n">
-        <v>6542420</v>
+        <v>6542410</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1850,41 +1848,43 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126600806</v>
+        <v>126600795</v>
       </c>
       <c r="B13" t="n">
-        <v>75127</v>
+        <v>5196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>105930</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1892,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507912</v>
+        <v>507919</v>
       </c>
       <c r="R13" t="n">
-        <v>6542410</v>
+        <v>6542420</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2597,7 +2597,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126600741</v>
+        <v>126600750</v>
       </c>
       <c r="B20" t="n">
         <v>8447</v>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507957</v>
+        <v>507956</v>
       </c>
       <c r="R20" t="n">
-        <v>6542483</v>
+        <v>6542468</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2704,7 +2704,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126600750</v>
+        <v>126600741</v>
       </c>
       <c r="B21" t="n">
         <v>8447</v>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507956</v>
+        <v>507957</v>
       </c>
       <c r="R21" t="n">
-        <v>6542468</v>
+        <v>6542483</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3349,7 +3349,7 @@
         <v>126671977</v>
       </c>
       <c r="B27" t="n">
-        <v>57654</v>
+        <v>57660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>126674072</v>
       </c>
       <c r="B28" t="n">
-        <v>56849</v>
+        <v>56855</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>126674690</v>
       </c>
       <c r="B29" t="n">
-        <v>57654</v>
+        <v>57660</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 34275-2025 artfynd.xlsx
+++ b/artfynd/A 34275-2025 artfynd.xlsx
@@ -675,43 +675,41 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126601061</v>
+        <v>126600806</v>
       </c>
       <c r="B2" t="n">
-        <v>8447</v>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507744</v>
+        <v>507912</v>
       </c>
       <c r="R2" t="n">
-        <v>6542221</v>
+        <v>6542410</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -782,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126600734</v>
+        <v>126600962</v>
       </c>
       <c r="B3" t="n">
-        <v>8447</v>
+        <v>97394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,32 +791,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>2590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -826,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507916</v>
+        <v>507910</v>
       </c>
       <c r="R3" t="n">
-        <v>6542579</v>
+        <v>6542329</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -892,7 +889,7 @@
         <v>126601043</v>
       </c>
       <c r="B4" t="n">
-        <v>96731</v>
+        <v>97394</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126600738</v>
+        <v>126670535</v>
       </c>
       <c r="B5" t="n">
-        <v>4772</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,46 +1003,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hageberg, Nrk</t>
+          <t>Olyckskärret, Olyckskärret, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507958</v>
+        <v>507927</v>
       </c>
       <c r="R5" t="n">
-        <v>6542499</v>
+        <v>6542513</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1069,12 +1057,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,29 +1081,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126600426</v>
+        <v>126671977</v>
       </c>
       <c r="B6" t="n">
-        <v>8447</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1113,46 +1110,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hageberg, Nrk</t>
+          <t>Olyckskärret, Olyckskärret, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507668</v>
+        <v>507919</v>
       </c>
       <c r="R6" t="n">
-        <v>6542310</v>
+        <v>6542485</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,12 +1169,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,29 +1193,53 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126600779</v>
+        <v>126674690</v>
       </c>
       <c r="B7" t="n">
-        <v>4772</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1220,46 +1247,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hageberg, Nrk</t>
+          <t>Dalhultet, Dalhultet, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>507911</v>
+        <v>507937</v>
       </c>
       <c r="R7" t="n">
-        <v>6542433</v>
+        <v>6542286</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1283,12 +1306,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färska hack i död högstubbe björk</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,29 +1335,53 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Betula</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126600699</v>
+        <v>126674072</v>
       </c>
       <c r="B8" t="n">
-        <v>8447</v>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,46 +1389,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hageberg, Nrk</t>
+          <t>Hageberg, Hageberg, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>507819</v>
+        <v>507662</v>
       </c>
       <c r="R8" t="n">
-        <v>6542586</v>
+        <v>6542223</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1390,12 +1457,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Uppskrämd från marken</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,29 +1486,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126601064</v>
+        <v>126600693</v>
       </c>
       <c r="B9" t="n">
-        <v>8447</v>
+        <v>4775</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1434,21 +1520,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1553,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>507727</v>
+        <v>507845</v>
       </c>
       <c r="R9" t="n">
-        <v>6542229</v>
+        <v>6542442</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1530,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126600550</v>
+        <v>126600738</v>
       </c>
       <c r="B10" t="n">
-        <v>5176</v>
+        <v>4775</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1541,21 +1627,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1574,10 +1660,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>507743</v>
+        <v>507958</v>
       </c>
       <c r="R10" t="n">
-        <v>6542302</v>
+        <v>6542499</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1637,10 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126600962</v>
+        <v>126600768</v>
       </c>
       <c r="B11" t="n">
-        <v>96731</v>
+        <v>4775</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,31 +1734,32 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2590</v>
+        <v>100299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>507910</v>
+        <v>507950</v>
       </c>
       <c r="R11" t="n">
-        <v>6542329</v>
+        <v>6542418</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1743,41 +1830,43 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126600806</v>
+        <v>126600779</v>
       </c>
       <c r="B12" t="n">
-        <v>75130</v>
+        <v>4775</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>308</v>
+        <v>100299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1785,10 +1874,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>507912</v>
+        <v>507911</v>
       </c>
       <c r="R12" t="n">
-        <v>6542410</v>
+        <v>6542433</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1848,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126600795</v>
+        <v>126600550</v>
       </c>
       <c r="B13" t="n">
-        <v>5196</v>
+        <v>5179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,21 +1948,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1892,10 +1981,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>507919</v>
+        <v>507743</v>
       </c>
       <c r="R13" t="n">
-        <v>6542420</v>
+        <v>6542302</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1955,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126601040</v>
+        <v>126600761</v>
       </c>
       <c r="B14" t="n">
-        <v>8447</v>
+        <v>6274</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1966,32 +2055,32 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>105336</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vanlig flatbagge</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Peltis ferruginea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1999,10 +2088,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>507921</v>
+        <v>507954</v>
       </c>
       <c r="R14" t="n">
-        <v>6542284</v>
+        <v>6542455</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2062,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126600761</v>
+        <v>126600873</v>
       </c>
       <c r="B15" t="n">
-        <v>6271</v>
+        <v>6274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,10 +2195,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>507954</v>
+        <v>507957</v>
       </c>
       <c r="R15" t="n">
-        <v>6542455</v>
+        <v>6542361</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2169,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126600693</v>
+        <v>126600795</v>
       </c>
       <c r="B16" t="n">
-        <v>4772</v>
+        <v>5199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2180,21 +2269,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,10 +2302,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>507845</v>
+        <v>507919</v>
       </c>
       <c r="R16" t="n">
-        <v>6542442</v>
+        <v>6542420</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2276,10 +2365,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126600768</v>
+        <v>126600426</v>
       </c>
       <c r="B17" t="n">
-        <v>4772</v>
+        <v>8455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2287,21 +2376,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100299</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2320,10 +2409,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>507950</v>
+        <v>507668</v>
       </c>
       <c r="R17" t="n">
-        <v>6542418</v>
+        <v>6542310</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2386,7 +2475,7 @@
         <v>126600691</v>
       </c>
       <c r="B18" t="n">
-        <v>8447</v>
+        <v>8455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2490,10 +2579,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126600727</v>
+        <v>126600697</v>
       </c>
       <c r="B19" t="n">
-        <v>8447</v>
+        <v>8455</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2534,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>507843</v>
+        <v>507831</v>
       </c>
       <c r="R19" t="n">
-        <v>6542576</v>
+        <v>6542470</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2597,10 +2686,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126600750</v>
+        <v>126600699</v>
       </c>
       <c r="B20" t="n">
-        <v>8447</v>
+        <v>8455</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,10 +2730,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>507956</v>
+        <v>507819</v>
       </c>
       <c r="R20" t="n">
-        <v>6542468</v>
+        <v>6542586</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2704,10 +2793,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126600741</v>
+        <v>126600727</v>
       </c>
       <c r="B21" t="n">
-        <v>8447</v>
+        <v>8455</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2748,10 +2837,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>507957</v>
+        <v>507843</v>
       </c>
       <c r="R21" t="n">
-        <v>6542483</v>
+        <v>6542576</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2811,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126600697</v>
+        <v>126600734</v>
       </c>
       <c r="B22" t="n">
-        <v>8447</v>
+        <v>8455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2855,10 +2944,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>507831</v>
+        <v>507916</v>
       </c>
       <c r="R22" t="n">
-        <v>6542470</v>
+        <v>6542579</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2918,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126600873</v>
+        <v>126600741</v>
       </c>
       <c r="B23" t="n">
-        <v>6271</v>
+        <v>8455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2929,32 +3018,32 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>105336</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vanlig flatbagge</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Peltis ferruginea</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2965,7 +3054,7 @@
         <v>507957</v>
       </c>
       <c r="R23" t="n">
-        <v>6542361</v>
+        <v>6542483</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3025,10 +3114,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126600785</v>
+        <v>126600750</v>
       </c>
       <c r="B24" t="n">
-        <v>8447</v>
+        <v>8455</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3069,10 +3158,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>507909</v>
+        <v>507956</v>
       </c>
       <c r="R24" t="n">
-        <v>6542421</v>
+        <v>6542468</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3132,10 +3221,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126600902</v>
+        <v>126600785</v>
       </c>
       <c r="B25" t="n">
-        <v>8447</v>
+        <v>8455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3176,10 +3265,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>507934</v>
+        <v>507909</v>
       </c>
       <c r="R25" t="n">
-        <v>6542308</v>
+        <v>6542421</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3239,48 +3328,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126670535</v>
+        <v>126600902</v>
       </c>
       <c r="B26" t="n">
-        <v>57654</v>
+        <v>8455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Olyckskärret, Olyckskärret, Nrk</t>
+          <t>Hageberg, Nrk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>507927</v>
+        <v>507934</v>
       </c>
       <c r="R26" t="n">
-        <v>6542513</v>
+        <v>6542308</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3304,22 +3402,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:25</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>10:25</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3328,71 +3416,76 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126671977</v>
+        <v>126601040</v>
       </c>
       <c r="B27" t="n">
-        <v>57660</v>
+        <v>8455</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Olyckskärret, Olyckskärret, Nrk</t>
+          <t>Hageberg, Nrk</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>507919</v>
+        <v>507921</v>
       </c>
       <c r="R27" t="n">
-        <v>6542485</v>
+        <v>6542284</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3416,22 +3509,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:17</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3440,53 +3523,29 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126674072</v>
+        <v>126601061</v>
       </c>
       <c r="B28" t="n">
-        <v>56855</v>
+        <v>8455</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3494,51 +3553,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hageberg, Hageberg, Nrk</t>
+          <t>Hageberg, Nrk</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>507662</v>
+        <v>507744</v>
       </c>
       <c r="R28" t="n">
-        <v>6542223</v>
+        <v>6542221</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3562,27 +3616,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Uppskrämd från marken</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3591,76 +3630,76 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126674690</v>
+        <v>126601064</v>
       </c>
       <c r="B29" t="n">
-        <v>57660</v>
+        <v>8455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dalhultet, Dalhultet, Nrk</t>
+          <t>Hageberg, Nrk</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>507937</v>
+        <v>507727</v>
       </c>
       <c r="R29" t="n">
-        <v>6542286</v>
+        <v>6542229</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3684,27 +3723,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>12:31</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Färska hack i död högstubbe björk</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3713,43 +3737,19 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Betula</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 34275-2025 artfynd.xlsx
+++ b/artfynd/A 34275-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600806</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600962</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601043</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126670535</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126671977</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1375,6 +1405,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126674690</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1506,6 +1541,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126674072</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1613,6 +1653,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600693</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1720,6 +1765,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600738</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1827,6 +1877,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600768</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1934,6 +1989,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600779</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2041,6 +2101,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600550</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2148,6 +2213,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600761</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2255,6 +2325,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600873</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2362,6 +2437,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600795</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2469,6 +2549,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600426</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2576,6 +2661,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600691</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2683,6 +2773,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600697</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2790,6 +2885,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600699</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2897,6 +2997,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600727</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3004,6 +3109,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600734</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3111,6 +3221,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600741</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3218,6 +3333,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600750</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3325,6 +3445,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600785</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3432,6 +3557,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126600902</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3539,6 +3669,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601040</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3646,6 +3781,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601061</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3753,8 +3893,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126601064</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>